--- a/cellstocks/cell-stocks.xlsx
+++ b/cellstocks/cell-stocks.xlsx
@@ -1588,6 +1588,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1665,6 +1670,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1742,6 +1752,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1819,6 +1834,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1896,6 +1916,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1973,6 +1998,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2050,6 +2080,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2127,6 +2162,11 @@
           <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2204,6 +2244,11 @@
           <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2281,6 +2326,11 @@
           <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2358,6 +2408,11 @@
           <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2435,6 +2490,11 @@
           <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2512,6 +2572,11 @@
           <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -6451,6 +6516,11 @@
           <t xml:space="preserve">20-07-26</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -10894,6 +10964,11 @@
           <t xml:space="preserve">15-11-25</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -10971,6 +11046,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -11048,6 +11128,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -14840,6 +14925,11 @@
           <t xml:space="preserve">31-07-25</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -17589,6 +17679,11 @@
       <c r="I213" t="inlineStr">
         <is>
           <t xml:space="preserve">30-05-25</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -33683,6 +33778,90 @@
         <v>81</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LN2 Tank</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ln2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tower 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Box 1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>81</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LN2 Tank</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ln2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tower 1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Box 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>81</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/cell-stocks.xlsx
+++ b/cellstocks/cell-stocks.xlsx
@@ -184,14 +184,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -266,14 +266,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -348,14 +348,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -430,14 +430,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -512,14 +512,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-09</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">9/4/2026</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -594,14 +594,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-09</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">9/4/2026</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -840,14 +840,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-10</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">10/2/2026</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1578,14 +1578,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1660,14 +1660,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1742,14 +1742,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1824,14 +1824,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1906,14 +1906,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-07</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1988,14 +1988,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-07</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2070,14 +2070,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-07</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3176,14 +3176,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-02-03</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">3/2/2023</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3340,14 +3340,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3750,14 +3750,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-06</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">6/2/2026</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3914,14 +3914,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-05</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">5/2/2026</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3996,14 +3996,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4160,14 +4160,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4324,14 +4324,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-03</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">3/3/2026</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4406,14 +4406,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-03</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">3/3/2026</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5686,14 +5686,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5850,14 +5850,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6096,14 +6096,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6178,14 +6178,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6834,14 +6834,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-10</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6916,14 +6916,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-11</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6998,14 +6998,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-11</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7080,14 +7080,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-10</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -7244,14 +7244,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-07</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">7/7/2025</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7336,14 +7336,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-09</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">9/6/2026</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7500,14 +7500,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-09</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">9/6/2026</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7582,14 +7582,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-08</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2026</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8402,14 +8402,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-10</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8484,14 +8484,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-10</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8566,14 +8566,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-06-02</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">2/6/2025</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8658,14 +8658,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-08</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2026</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -8822,14 +8822,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-09</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8904,14 +8904,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-09</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -8986,14 +8986,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-09</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9396,14 +9396,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -9478,14 +9478,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -9724,14 +9724,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-06</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">6/1/2025</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10298,14 +10298,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -10380,14 +10380,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">11/12/2025</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -10462,14 +10462,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-07</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr">
         <is>
           <t xml:space="preserve">7/10/2025</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -11036,14 +11036,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -11118,14 +11118,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11200,14 +11200,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-07</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
           <t xml:space="preserve">7/10/2025</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11446,14 +11446,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -11528,14 +11528,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -11610,14 +11610,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -11692,14 +11692,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -11774,14 +11774,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11856,14 +11856,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -11938,14 +11938,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-10</t>
+        </is>
+      </c>
       <c r="I144" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -13347,14 +13347,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -13439,14 +13439,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I162" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -14177,14 +14177,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-08-11</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr">
         <is>
           <t xml:space="preserve">11/8/2025</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -14341,14 +14341,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -14423,14 +14423,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -14505,14 +14505,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -14587,14 +14587,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -14669,14 +14669,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -14751,14 +14751,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -14833,14 +14833,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -15775,14 +15775,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -15857,14 +15857,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -16103,14 +16103,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-06-02</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr">
         <is>
           <t xml:space="preserve">2/6/2025</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -16185,14 +16185,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -16513,14 +16513,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-04</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr">
         <is>
           <t xml:space="preserve">4/11/2025</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -16677,14 +16677,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-04</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr">
         <is>
           <t xml:space="preserve">4/11/2025</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -17753,14 +17753,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-04</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -17845,14 +17845,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-04</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -18593,14 +18593,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-01-05</t>
+        </is>
+      </c>
       <c r="I224" t="inlineStr">
         <is>
           <t xml:space="preserve">5/1/2024</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -18921,14 +18921,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-04-05</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr">
         <is>
           <t xml:space="preserve">5/4/2024</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -19249,14 +19249,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I232" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -19577,14 +19577,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-05</t>
+        </is>
+      </c>
       <c r="I236" t="inlineStr">
         <is>
           <t xml:space="preserve">5/3/2026</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -19659,14 +19659,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -19741,14 +19741,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -19823,14 +19823,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I239" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -20141,14 +20141,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-06</t>
+        </is>
+      </c>
       <c r="I243" t="inlineStr">
         <is>
           <t xml:space="preserve">6/11/2025</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20305,14 +20305,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-06</t>
+        </is>
+      </c>
       <c r="I245" t="inlineStr">
         <is>
           <t xml:space="preserve">6/11/2025</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20464,14 +20464,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I247" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20546,14 +20546,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20628,14 +20628,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -20710,14 +20710,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -20874,14 +20874,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
       <c r="I252" t="inlineStr">
         <is>
           <t xml:space="preserve">11/12/2025</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -21120,14 +21120,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
       <c r="I255" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21202,14 +21202,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-10</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -21284,14 +21284,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I257" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21366,14 +21366,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I258" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21448,14 +21448,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I259" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -21530,14 +21530,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I260" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21612,14 +21612,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -21694,14 +21694,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-02</t>
+        </is>
+      </c>
       <c r="I262" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -21776,14 +21776,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
       <c r="I263" t="inlineStr">
         <is>
           <t xml:space="preserve">4/12/2025</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -21858,14 +21858,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
       <c r="I264" t="inlineStr">
         <is>
           <t xml:space="preserve">4/12/2025</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -21940,14 +21940,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
       <c r="I265" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -22022,14 +22022,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-02</t>
+        </is>
+      </c>
       <c r="I266" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -22104,14 +22104,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-02</t>
+        </is>
+      </c>
       <c r="I267" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -22842,14 +22842,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
       <c r="I276" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -22924,14 +22924,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
       <c r="I277" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -23006,14 +23006,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
       <c r="I278" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23088,14 +23088,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I279" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23580,14 +23580,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I285" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -24149,14 +24149,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-05</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t xml:space="preserve">5/1/2026</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24477,14 +24477,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I296" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24559,14 +24559,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I297" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24641,14 +24641,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I298" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24723,14 +24723,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I299" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24805,14 +24805,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I300" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24887,14 +24887,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I301" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24969,14 +24969,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I302" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -25297,14 +25297,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I306" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25379,14 +25379,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I307" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25461,14 +25461,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I308" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25543,14 +25543,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I309" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25625,14 +25625,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I310" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -26035,14 +26035,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
       <c r="I315" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26117,14 +26117,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I316" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26199,14 +26199,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I317" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26281,14 +26281,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I318" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26363,14 +26363,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I319" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26445,14 +26445,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I320" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26527,14 +26527,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I321" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26691,14 +26691,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
       <c r="I323" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -27039,14 +27039,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-04</t>
+        </is>
+      </c>
       <c r="I327" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27608,14 +27608,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I334" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27772,14 +27772,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I336" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27854,14 +27854,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I337" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27936,14 +27936,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I338" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -28018,14 +28018,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-10</t>
+        </is>
+      </c>
       <c r="I339" t="inlineStr">
         <is>
           <t xml:space="preserve">10/2/2026</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28182,14 +28182,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-06</t>
+        </is>
+      </c>
       <c r="I341" t="inlineStr">
         <is>
           <t xml:space="preserve">6/2/2026</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">

--- a/cellstocks/cell-stocks.xlsx
+++ b/cellstocks/cell-stocks.xlsx
@@ -21184,17 +21184,17 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-355</t>
+          <t xml:space="preserve">v-356</t>
         </is>
       </c>
     </row>
@@ -21266,12 +21266,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -21301,7 +21301,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-356</t>
+          <t xml:space="preserve">v-357</t>
         </is>
       </c>
     </row>
@@ -21348,17 +21348,17 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 OX rep 3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-357</t>
+          <t xml:space="preserve">v-358</t>
         </is>
       </c>
     </row>
@@ -21430,57 +21430,57 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-358</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21512,32 +21512,32 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -21594,12 +21594,12 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -21676,32 +21676,32 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21778,12 +21778,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -21922,52 +21922,52 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22004,12 +22004,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22086,17 +22086,17 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -22106,17 +22106,17 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22163,22 +22163,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -22188,37 +22188,37 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22332,32 +22332,32 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22414,22 +22414,22 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22578,17 +22578,17 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -22598,12 +22598,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -22660,17 +22660,17 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -22742,22 +22742,22 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22802,7 +22802,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -22824,32 +22824,32 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -22906,57 +22906,57 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23070,12 +23070,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -23212,7 +23212,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23234,17 +23234,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23254,12 +23254,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23316,17 +23316,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -23336,12 +23336,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23398,17 +23398,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23480,12 +23480,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -23644,17 +23644,17 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -23662,14 +23662,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23679,7 +23674,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23694,7 +23689,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23704,7 +23699,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -23726,7 +23721,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -23736,7 +23731,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23744,9 +23739,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -23803,39 +23803,39 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -23885,17 +23885,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23905,12 +23905,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23945,7 +23945,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -23967,17 +23967,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23987,12 +23987,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24027,7 +24027,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24049,12 +24049,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24084,7 +24084,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24213,32 +24213,32 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24248,7 +24248,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24295,22 +24295,22 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -24330,7 +24330,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24377,57 +24377,57 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24459,22 +24459,22 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24541,22 +24541,22 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -24623,22 +24623,22 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -24658,22 +24658,22 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -24787,57 +24787,57 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -24869,22 +24869,22 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -24951,32 +24951,32 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25033,32 +25033,32 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25115,17 +25115,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25135,37 +25135,37 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25175,7 +25175,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25197,12 +25197,12 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -25232,7 +25232,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25279,12 +25279,12 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -25396,7 +25396,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25443,32 +25443,32 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25525,22 +25525,22 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -25607,32 +25607,32 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25667,7 +25667,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -25689,32 +25689,32 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -25771,17 +25771,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25791,12 +25791,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -25853,17 +25853,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25873,17 +25873,17 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -25935,7 +25935,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26017,17 +26017,17 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26099,7 +26099,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -26159,7 +26159,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26181,17 +26181,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26216,7 +26216,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26263,22 +26263,22 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26323,7 +26323,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26345,17 +26345,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26365,12 +26365,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26405,7 +26405,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -26437,7 +26437,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -26447,12 +26447,12 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26487,7 +26487,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26509,32 +26509,32 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26569,7 +26569,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -26591,37 +26591,37 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -26641,7 +26641,17 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26651,7 +26661,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -26673,7 +26683,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -26743,7 +26753,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -26765,17 +26775,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26785,12 +26795,12 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26815,17 +26825,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -26857,7 +26857,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -26867,7 +26867,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26877,12 +26877,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26917,7 +26917,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -26939,32 +26939,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27021,12 +27021,12 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -27081,7 +27081,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27103,12 +27103,12 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -27163,7 +27163,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27185,17 +27185,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p45769</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27203,14 +27203,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27220,7 +27215,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27230,7 +27225,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -27245,7 +27240,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27267,27 +27262,32 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27344,42 +27344,42 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27389,12 +27389,12 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27404,7 +27404,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27426,17 +27426,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27446,12 +27446,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27508,17 +27508,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27528,12 +27528,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27568,7 +27568,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -27590,17 +27590,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -27672,7 +27672,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -27754,32 +27754,32 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27799,12 +27799,12 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -27836,32 +27836,32 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27881,12 +27881,12 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -27918,17 +27918,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27938,12 +27938,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27953,7 +27953,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28000,17 +28000,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -28020,12 +28020,12 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28082,57 +28082,57 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28142,7 +28142,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28164,7 +28164,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -28174,7 +28174,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -28184,12 +28184,12 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28246,7 +28246,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28328,7 +28328,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -28388,7 +28388,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28410,7 +28410,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28492,7 +28492,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -28574,32 +28574,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28609,22 +28609,22 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -28656,39 +28656,39 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p218</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -28696,7 +28696,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">50CR</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -28738,17 +28738,17 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p218</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28773,22 +28773,22 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28798,39 +28798,19 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-80 °C Freezer</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p23</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -28840,59 +28820,59 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-243</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p23</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28902,12 +28882,12 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28917,7 +28897,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -28942,19 +28922,19 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-243</t>
+          <t xml:space="preserve">v-331</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -28974,12 +28954,12 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -28994,7 +28974,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29004,7 +28984,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-331</t>
+          <t xml:space="preserve">v-355</t>
         </is>
       </c>
     </row>
@@ -30683,12 +30663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LCC-V</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -30698,7 +30673,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E55">
@@ -30714,7 +30689,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -30740,7 +30715,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LUCX gP2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -30750,7 +30730,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E57">
@@ -30760,18 +30740,18 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -30781,7 +30761,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E58">
@@ -30797,7 +30777,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -30807,7 +30787,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -30828,7 +30808,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -30838,7 +30818,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -30859,7 +30839,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -30869,7 +30849,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -30884,13 +30864,13 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -30915,13 +30895,13 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -30946,13 +30926,13 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -30977,23 +30957,23 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -31002,7 +30982,7 @@
         </is>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -31014,7 +30994,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -31024,7 +31004,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -31045,7 +31025,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -31055,12 +31035,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E67">
@@ -31076,22 +31056,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E68">
@@ -31107,7 +31087,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -31117,12 +31097,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E69">
@@ -31138,7 +31118,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -31148,12 +31128,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E70">
@@ -31169,7 +31149,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31179,12 +31159,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E71">
@@ -31200,7 +31180,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31231,7 +31211,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31241,7 +31221,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -31262,7 +31242,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -31293,7 +31273,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -31324,7 +31304,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -31355,7 +31335,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -31386,7 +31366,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -31417,7 +31397,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -31427,7 +31407,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -31448,7 +31428,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -31479,7 +31459,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -31510,7 +31490,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -31520,12 +31500,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E82">
@@ -31541,7 +31521,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -31551,12 +31531,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E83">
@@ -31572,7 +31552,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -31582,12 +31562,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E84">
@@ -31603,7 +31583,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -31613,12 +31593,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E85">
@@ -31634,7 +31614,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -31649,7 +31629,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E86">
@@ -31665,7 +31645,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -31696,7 +31676,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -31711,7 +31691,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E88">
@@ -31727,7 +31707,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -31742,7 +31722,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E89">
@@ -31758,7 +31738,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -31789,7 +31769,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -31804,7 +31784,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E91">
@@ -31820,7 +31800,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -31835,7 +31815,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E92">
@@ -31851,7 +31831,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -31866,7 +31846,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E93">
@@ -31882,7 +31862,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -31897,7 +31877,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E94">
@@ -31913,7 +31893,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -31928,7 +31908,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E95">
@@ -31944,7 +31924,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -31959,7 +31939,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E96">
@@ -31975,7 +31955,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -32006,7 +31986,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -32021,7 +32001,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E98">
@@ -32037,7 +32017,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -32047,12 +32027,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E99">
@@ -32068,7 +32048,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -32078,12 +32058,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E100">
@@ -32099,7 +32079,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -32109,12 +32089,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E101">
@@ -32130,17 +32110,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -32161,7 +32141,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -32192,7 +32172,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -32202,7 +32182,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -32223,7 +32203,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -32254,7 +32234,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -32264,7 +32244,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -32285,7 +32265,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -32316,7 +32296,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -32326,12 +32306,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E108">
@@ -32347,7 +32327,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -32357,12 +32337,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E109">
@@ -32378,7 +32358,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -32393,7 +32373,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E110">
@@ -32409,7 +32389,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -32419,12 +32399,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E111">
@@ -32440,7 +32420,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -32450,12 +32430,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E112">
@@ -32471,7 +32451,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -32481,12 +32461,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E113">
@@ -32502,7 +32482,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -32512,7 +32492,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -32533,7 +32513,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -32543,7 +32523,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -32564,7 +32544,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 OX rep 3</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -32574,12 +32554,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E116">
@@ -32595,7 +32575,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -32626,7 +32606,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -32641,7 +32621,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E118">
@@ -32657,7 +32637,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -32672,7 +32652,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E119">
@@ -32688,7 +32668,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -32698,12 +32678,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E120">
@@ -32719,7 +32699,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -32729,19 +32709,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E121">
         <v>1</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -33521,6 +33501,53 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 °C Freezer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut iphone cell stocks</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-355</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -33784,10 +33811,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J6">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/cell-stocks.xlsx
+++ b/cellstocks/cell-stocks.xlsx
@@ -19641,17 +19641,17 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">p26</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -19659,14 +19659,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -19676,7 +19671,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19701,7 +19696,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-330</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -19723,7 +19718,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19778,7 +19773,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -19800,7 +19795,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19810,7 +19805,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -19818,9 +19813,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-27</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -19897,12 +19897,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -19979,12 +19979,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -20041,7 +20041,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -20061,12 +20061,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20141,14 +20141,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/11/2025</t>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20183,7 +20178,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20205,17 +20200,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -20223,14 +20218,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20548,12 +20548,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -20610,57 +20610,57 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -20692,32 +20692,32 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -20727,22 +20727,22 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -20856,57 +20856,57 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -20938,17 +20938,17 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -20958,37 +20958,37 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -21040,12 +21040,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21102,57 +21102,57 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21184,17 +21184,17 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -21204,37 +21204,37 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-356</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -21266,17 +21266,17 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 OX rep 3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -21286,37 +21286,37 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-357</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -21348,57 +21348,57 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-358</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -21430,12 +21430,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -21512,32 +21512,32 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -21594,17 +21594,17 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -21614,37 +21614,37 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -21676,57 +21676,57 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -21758,57 +21758,57 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -21835,37 +21835,37 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -21917,22 +21917,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -21942,37 +21942,37 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -21999,62 +21999,62 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22081,62 +22081,62 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22168,32 +22168,32 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22250,32 +22250,32 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -22332,32 +22332,32 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -22414,32 +22414,32 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -22496,17 +22496,17 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -22516,12 +22516,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -22578,57 +22578,57 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -22660,57 +22660,57 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -22742,17 +22742,17 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -22762,37 +22762,37 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22802,7 +22802,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -22824,57 +22824,57 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -22906,17 +22906,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22926,12 +22926,12 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -22988,17 +22988,17 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -23008,12 +23008,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23070,17 +23070,17 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -23090,12 +23090,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23152,17 +23152,17 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -23172,12 +23172,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23212,7 +23212,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23234,12 +23234,12 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -23316,17 +23316,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -23334,14 +23334,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23351,7 +23346,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -23366,7 +23361,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23376,7 +23371,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -23398,12 +23393,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -23433,7 +23428,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -23448,7 +23443,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23458,7 +23453,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -23480,12 +23475,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -23515,7 +23510,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -23530,7 +23525,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23540,7 +23535,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -23562,17 +23557,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -23582,12 +23577,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23612,7 +23607,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23622,7 +23617,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -23644,34 +23639,39 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK gNT(20)</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p13</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-14</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-01-26</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -23689,7 +23689,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -23721,42 +23721,42 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p13</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-14</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-01-26</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -23803,17 +23803,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23823,12 +23823,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23838,7 +23838,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -23885,32 +23885,32 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23945,7 +23945,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -23967,17 +23967,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23987,12 +23987,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24027,7 +24027,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24049,57 +24049,57 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24131,17 +24131,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24151,37 +24151,37 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24213,17 +24213,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24233,37 +24233,37 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -24295,17 +24295,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24315,22 +24315,22 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -24377,22 +24377,22 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -24412,22 +24412,22 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -24459,32 +24459,32 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -24541,32 +24541,32 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -24623,57 +24623,57 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+12</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -24705,57 +24705,57 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p10</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/5/2025</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -24787,57 +24787,57 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -24869,17 +24869,17 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -24889,37 +24889,37 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -24951,57 +24951,57 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25033,17 +25033,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -25053,37 +25053,37 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25115,32 +25115,32 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25150,7 +25150,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -25175,7 +25175,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25197,17 +25197,17 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25217,12 +25217,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -25279,32 +25279,32 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">caNT read</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -25361,17 +25361,17 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -25381,12 +25381,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -25443,32 +25443,32 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -25525,17 +25525,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25545,17 +25545,17 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -25607,37 +25607,37 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -25667,7 +25667,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -25689,17 +25689,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25709,22 +25709,22 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -25771,17 +25771,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25791,22 +25791,22 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -25853,17 +25853,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -25935,22 +25935,22 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26017,32 +26017,32 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26099,32 +26099,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26159,7 +26159,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26181,17 +26181,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26201,12 +26201,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26216,7 +26216,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -26263,17 +26263,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -26283,22 +26283,22 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26313,7 +26313,17 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26323,7 +26333,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -26345,17 +26355,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26365,22 +26375,22 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26395,7 +26405,17 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26405,7 +26425,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -26427,17 +26447,17 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -26447,22 +26467,22 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26477,7 +26497,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26487,7 +26507,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -26509,37 +26529,37 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -26559,7 +26579,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26569,7 +26589,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -26591,32 +26611,32 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26641,17 +26661,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26661,7 +26671,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -26683,32 +26693,32 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -26733,17 +26743,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26753,7 +26753,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -26775,32 +26775,32 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -26857,32 +26857,27 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p45769</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-26</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26892,7 +26887,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26902,12 +26897,12 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26917,7 +26912,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -26939,32 +26934,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26974,7 +26969,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26984,7 +26979,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -26999,7 +26994,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27021,17 +27016,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27041,22 +27036,22 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27071,7 +27066,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27081,7 +27076,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27103,17 +27098,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27123,22 +27118,22 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27153,7 +27148,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27163,7 +27158,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27185,17 +27180,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27203,19 +27198,24 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27225,12 +27225,12 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -27262,42 +27262,42 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27307,7 +27307,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -27344,17 +27344,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27404,7 +27404,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -27426,32 +27426,32 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27471,12 +27471,12 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -27508,17 +27508,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27528,12 +27528,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27568,7 +27568,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -27590,17 +27590,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27610,12 +27610,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -27672,17 +27672,17 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -27692,12 +27692,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -27754,37 +27754,37 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -27836,57 +27836,57 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -27918,57 +27918,57 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28000,57 +28000,57 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28082,7 +28082,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28102,12 +28102,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28142,7 +28142,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28164,7 +28164,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -28246,32 +28246,32 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28281,22 +28281,22 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -28328,32 +28328,32 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuPar50CR+1</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p218</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28363,22 +28363,22 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">50CR</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28388,7 +28388,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -28410,32 +28410,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28470,347 +28470,267 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-80 °C Freezer</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I6</t>
-        </is>
-      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p23</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-243</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-80 °C Freezer</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I7</t>
-        </is>
-      </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p26</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-330</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="E347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/8/2026</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3xFLAG</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-331</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="E348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/8/2026</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
           <t xml:space="preserve">WT</t>
         </is>
       </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-161</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-80 °C Freezer</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I8</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p218</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50CR</t>
-        </is>
-      </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-162</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-80 °C Freezer</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p8</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CASPEX</t>
-        </is>
-      </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-355</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p23</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -28820,17 +28740,17 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -28860,19 +28780,19 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-243</t>
+          <t xml:space="preserve">v-356</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28892,12 +28812,12 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -28922,14 +28842,14 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-331</t>
+          <t xml:space="preserve">v-357</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -28959,7 +28879,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -28974,7 +28894,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -28984,7 +28904,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-355</t>
+          <t xml:space="preserve">v-358</t>
         </is>
       </c>
     </row>
@@ -30601,7 +30521,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -30611,7 +30531,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -30626,23 +30546,18 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LCC-V</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -30657,13 +30572,13 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -30689,7 +30604,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LUCX gP2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -30699,7 +30619,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E56">
@@ -30709,18 +30629,18 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -30730,7 +30650,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E57">
@@ -30746,7 +30666,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -30756,7 +30676,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -30777,7 +30697,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -30787,7 +30707,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -30808,7 +30728,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -30818,7 +30738,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -30833,13 +30753,13 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -30864,13 +30784,13 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -30895,13 +30815,13 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -30926,23 +30846,23 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -30951,7 +30871,7 @@
         </is>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -30963,7 +30883,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -30973,7 +30893,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -30994,7 +30914,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -31004,12 +30924,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E66">
@@ -31025,22 +30945,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E67">
@@ -31056,7 +30976,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -31066,12 +30986,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E68">
@@ -31087,7 +31007,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -31097,12 +31017,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E69">
@@ -31118,7 +31038,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -31128,12 +31048,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E70">
@@ -31149,7 +31069,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31180,7 +31100,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31190,7 +31110,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -31211,7 +31131,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31242,7 +31162,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -31273,7 +31193,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -31304,7 +31224,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -31335,7 +31255,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -31345,7 +31265,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -31366,7 +31286,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -31376,7 +31296,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -31397,7 +31317,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -31428,7 +31348,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -31438,12 +31358,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E80">
@@ -31459,7 +31379,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -31474,7 +31394,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E81">
@@ -31490,7 +31410,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -31500,12 +31420,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E82">
@@ -31521,7 +31441,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -31552,7 +31472,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -31562,12 +31482,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E84">
@@ -31583,7 +31503,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -31598,7 +31518,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E85">
@@ -31614,7 +31534,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -31629,7 +31549,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E86">
@@ -31645,7 +31565,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -31676,7 +31596,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -31691,7 +31611,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E88">
@@ -31707,7 +31627,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -31722,7 +31642,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E89">
@@ -31738,7 +31658,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -31769,7 +31689,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -31800,7 +31720,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -31831,7 +31751,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -31862,7 +31782,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -31893,7 +31813,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -31908,7 +31828,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E95">
@@ -31924,7 +31844,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -31939,7 +31859,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E96">
@@ -31955,7 +31875,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -31965,12 +31885,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E97">
@@ -31986,7 +31906,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -31996,12 +31916,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E98">
@@ -32017,7 +31937,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -32048,29 +31968,29 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -32079,17 +31999,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -32110,7 +32030,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -32141,7 +32061,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -32151,7 +32071,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -32172,7 +32092,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -32203,7 +32123,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -32213,7 +32133,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -32234,7 +32154,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -32265,7 +32185,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -32275,12 +32195,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E107">
@@ -32296,7 +32216,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -32306,12 +32226,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E108">
@@ -32327,7 +32247,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -32342,7 +32262,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E109">
@@ -32358,7 +32278,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -32368,12 +32288,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E110">
@@ -32389,7 +32309,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -32399,12 +32319,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E111">
@@ -32420,7 +32340,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -32430,12 +32350,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E112">
@@ -32451,7 +32371,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -32461,12 +32381,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E113">
@@ -32482,7 +32402,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -32497,7 +32417,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E114">
@@ -32513,7 +32433,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 OX rep 3</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -32523,12 +32443,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E115">
@@ -32544,7 +32464,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -32575,7 +32495,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -32585,12 +32505,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E117">
@@ -32606,7 +32526,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -32616,19 +32536,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E118">
         <v>1</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -32637,7 +32557,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 lef1 OX</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -32647,12 +32567,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E119">
@@ -32668,17 +32588,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LCC-C*</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -32699,12 +32614,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LCC-E</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -32714,14 +32624,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E121">
         <v>1</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -32730,17 +32640,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LCC-H</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -32761,7 +32666,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C*</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -32787,7 +32692,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -32813,7 +32718,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -32839,7 +32744,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LNCAP BMK</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -32865,7 +32775,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -32891,7 +32806,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -32917,7 +32837,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -32948,7 +32868,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -32979,7 +32899,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -33010,7 +32930,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -33041,7 +32961,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -33072,7 +32992,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -33082,7 +33002,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -33103,7 +33023,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -33113,7 +33033,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -33134,12 +33054,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -33165,22 +33085,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E137">
@@ -33196,22 +33116,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E138">
@@ -33227,17 +33147,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -33246,91 +33166,91 @@
         </is>
       </c>
       <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
         <v>1</v>
       </c>
-      <c r="F139">
+      <c r="G139">
         <v>0</v>
-      </c>
-      <c r="G139">
-        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
         <v>1</v>
       </c>
-      <c r="F140">
+      <c r="G140">
         <v>0</v>
-      </c>
-      <c r="G140">
-        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
         <v>1</v>
       </c>
-      <c r="F141">
+      <c r="G141">
         <v>0</v>
-      </c>
-      <c r="G141">
-        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -33548,6 +33468,194 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 °C Freezer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut iphone cell stocks</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-356</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 °C Freezer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut iphone cell stocks</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-357</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 °C Freezer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut iphone cell stocks</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-358</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 °C Freezer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut iphone cell stocks</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-330</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -33811,10 +33919,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/cell-stocks.xlsx
+++ b/cellstocks/cell-stocks.xlsx
@@ -19559,17 +19559,17 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -19577,14 +19577,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -19609,7 +19604,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -19619,7 +19614,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-329</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19636,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -19696,7 +19691,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -19718,7 +19713,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19728,7 +19723,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -19736,9 +19731,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-27</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -19795,7 +19795,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -19815,12 +19815,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -19897,12 +19897,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -19979,12 +19979,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20041,7 +20041,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -20059,14 +20059,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/11/2025</t>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -20101,7 +20096,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20123,17 +20118,17 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20141,14 +20136,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20466,12 +20466,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -20528,57 +20528,57 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -20610,32 +20610,32 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -20645,22 +20645,22 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -20774,57 +20774,57 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -20856,17 +20856,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -20876,37 +20876,37 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -20958,12 +20958,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21020,57 +21020,57 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21102,32 +21102,32 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -21184,12 +21184,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -21266,32 +21266,32 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -21368,12 +21368,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -21512,52 +21512,52 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -21594,12 +21594,12 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -21676,17 +21676,17 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -21696,17 +21696,17 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -21753,22 +21753,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -21778,37 +21778,37 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -21922,32 +21922,32 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22004,22 +22004,22 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22168,17 +22168,17 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -22188,12 +22188,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -22250,17 +22250,17 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -22332,22 +22332,22 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -22414,32 +22414,32 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -22496,57 +22496,57 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -22660,12 +22660,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -22802,7 +22802,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -22824,17 +22824,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22844,12 +22844,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -22906,17 +22906,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22926,12 +22926,12 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -22988,17 +22988,17 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -23008,12 +23008,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23070,12 +23070,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23152,12 +23152,12 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23212,7 +23212,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -23234,17 +23234,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23252,14 +23252,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23269,7 +23264,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -23284,7 +23279,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23294,7 +23289,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23311,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -23326,7 +23321,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -23334,9 +23329,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -23393,39 +23393,39 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -23443,7 +23443,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -23475,17 +23475,17 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -23495,12 +23495,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23510,7 +23510,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -23525,7 +23525,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -23557,17 +23557,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -23577,12 +23577,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -23639,12 +23639,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -23721,12 +23721,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -23803,32 +23803,32 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23838,7 +23838,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -23885,22 +23885,22 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23945,7 +23945,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -23967,57 +23967,57 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24027,7 +24027,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24049,22 +24049,22 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24131,22 +24131,22 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -24213,22 +24213,22 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -24248,22 +24248,22 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -24295,7 +24295,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -24377,57 +24377,57 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -24459,22 +24459,22 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -24541,32 +24541,32 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -24623,32 +24623,32 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -24705,17 +24705,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24725,37 +24725,37 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -24787,12 +24787,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -24869,12 +24869,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -24904,7 +24904,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -24951,12 +24951,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25033,32 +25033,32 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25115,22 +25115,22 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -25175,7 +25175,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -25197,32 +25197,32 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -25279,32 +25279,32 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -25361,17 +25361,17 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -25381,12 +25381,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -25443,17 +25443,17 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -25463,17 +25463,17 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -25525,7 +25525,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -25607,17 +25607,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25667,7 +25667,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -25771,17 +25771,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -25853,22 +25853,22 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -25935,17 +25935,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -25955,12 +25955,12 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -26027,7 +26027,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -26037,12 +26037,12 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26099,32 +26099,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26159,7 +26159,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -26181,37 +26181,37 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -26231,7 +26231,17 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26241,7 +26251,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -26263,7 +26273,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -26333,7 +26343,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -26355,17 +26365,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26375,12 +26385,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26405,17 +26415,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26425,7 +26425,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -26447,7 +26447,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -26467,12 +26467,12 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26507,7 +26507,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -26529,32 +26529,32 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -26611,12 +26611,12 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -26693,12 +26693,12 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -26753,7 +26753,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -26775,17 +26775,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p45769</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26793,14 +26793,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26810,7 +26805,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26820,7 +26815,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -26835,7 +26830,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -26857,27 +26852,32 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -26934,42 +26934,42 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26979,12 +26979,12 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27016,17 +27016,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27036,12 +27036,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27098,17 +27098,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27118,12 +27118,12 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27158,7 +27158,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -27180,17 +27180,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27230,7 +27230,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -27262,7 +27262,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -27344,32 +27344,32 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27389,12 +27389,12 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27404,7 +27404,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -27426,32 +27426,32 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27471,12 +27471,12 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -27508,17 +27508,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27528,12 +27528,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27568,7 +27568,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -27590,17 +27590,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27610,12 +27610,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -27672,57 +27672,57 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -27836,7 +27836,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -27918,7 +27918,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28000,7 +28000,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28082,7 +28082,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -28142,7 +28142,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -28164,32 +28164,32 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28199,22 +28199,22 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -28246,39 +28246,39 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p218</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">50CR</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -28328,17 +28328,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p218</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28363,22 +28363,22 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28388,39 +28388,19 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-80 °C Freezer</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p23</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28430,59 +28410,59 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-243</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p23</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28492,12 +28472,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28507,7 +28487,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -28522,7 +28502,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28532,7 +28512,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-243</t>
+          <t xml:space="preserve">v-329</t>
         </is>
       </c>
     </row>
@@ -29575,12 +29555,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -29590,7 +29570,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E22">
@@ -29600,18 +29580,18 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -29621,7 +29601,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E23">
@@ -29631,18 +29611,18 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LUCX gP1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -29652,7 +29632,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E24">
@@ -29662,32 +29642,32 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -29699,7 +29679,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -29709,19 +29689,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -33656,6 +33636,53 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 °C Freezer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut iphone cell stocks</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-329</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -33919,10 +33946,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/cell-stocks.xlsx
+++ b/cellstocks/cell-stocks.xlsx
@@ -26785,12 +26785,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
